--- a/order_forms/042_newsletter_subscription_management--order_forms.xlsx
+++ b/order_forms/042_newsletter_subscription_management--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>email_preferences</t>
+          <t>email_preferences_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Email Preferences</t>
+          <t>Email Preferences 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>delivery_frequency</t>
+          <t>delivery_frequency_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Delivery Frequency</t>
+          <t>Delivery Frequency 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -716,12 +716,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>start_date_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Start Date</t>
+          <t>Start Date 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>start_time_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Start Time</t>
+          <t>Start Time 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>end_date_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>End Date</t>
+          <t>End Date 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -958,12 +958,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>delivery_date</t>
+          <t>delivery_date_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Delivery Date</t>
+          <t>Delivery Date 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>delivery_time</t>
+          <t>delivery_time_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Delivery Time</t>
+          <t>Delivery Time 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1137,7 +1137,7 @@
   <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1162,7 +1162,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>email_preferences_choices</t>
+          <t>email_preferences_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>email_preferences_choices</t>
+          <t>email_preferences_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1196,7 +1196,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>email_preferences_choices</t>
+          <t>email_preferences_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1213,7 +1213,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>email_preferences_choices</t>
+          <t>email_preferences_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1230,7 +1230,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>email_preferences_choices</t>
+          <t>email_preferences_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1332,7 +1332,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>delivery_frequency_choices</t>
+          <t>delivery_frequency_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1349,7 +1349,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>delivery_frequency_choices</t>
+          <t>delivery_frequency_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1366,7 +1366,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>delivery_frequency_choices</t>
+          <t>delivery_frequency_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1383,7 +1383,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>delivery_frequency_choices</t>
+          <t>delivery_frequency_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1400,7 +1400,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>delivery_frequency_choices</t>
+          <t>delivery_frequency_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>start_date_choices</t>
+          <t>start_date_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1434,7 +1434,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>start_date_choices</t>
+          <t>start_date_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>start_date_choices</t>
+          <t>start_date_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1468,7 +1468,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>start_date_choices</t>
+          <t>start_date_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1485,7 +1485,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>start_date_choices</t>
+          <t>start_date_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1502,7 +1502,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>start_date_choices</t>
+          <t>start_date_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1536,7 +1536,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1604,7 +1604,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>start_time_choices</t>
+          <t>start_time_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>end_date_choices</t>
+          <t>end_date_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>end_date_choices</t>
+          <t>end_date_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>end_date_choices</t>
+          <t>end_date_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1672,7 +1672,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>end_date_choices</t>
+          <t>end_date_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1689,7 +1689,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>end_date_choices</t>
+          <t>end_date_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1706,7 +1706,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>end_date_choices</t>
+          <t>end_date_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1723,7 +1723,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>delivery_date_choices</t>
+          <t>delivery_date_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1740,7 +1740,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>delivery_date_choices</t>
+          <t>delivery_date_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1757,7 +1757,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>delivery_date_choices</t>
+          <t>delivery_date_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1774,7 +1774,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>delivery_date_choices</t>
+          <t>delivery_date_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1791,7 +1791,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>delivery_date_choices</t>
+          <t>delivery_date_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>delivery_date_choices</t>
+          <t>delivery_date_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1825,7 +1825,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>delivery_time_choices</t>
+          <t>delivery_time_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1842,7 +1842,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>delivery_time_choices</t>
+          <t>delivery_time_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>delivery_time_choices</t>
+          <t>delivery_time_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1876,7 +1876,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>delivery_time_choices</t>
+          <t>delivery_time_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1893,7 +1893,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>delivery_time_choices</t>
+          <t>delivery_time_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>delivery_time_choices</t>
+          <t>delivery_time_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
